--- a/output/CodeSystem-BRNomeExameLOINC.xlsx
+++ b/output/CodeSystem-BRNomeExameLOINC.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="880" uniqueCount="601">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="633">
   <si>
     <t>Property</t>
   </si>
@@ -468,6 +468,12 @@
     <t>SARS Coronavírus 2 [Presença de] em Amostra não específica por cultura em organismo específico</t>
   </si>
   <si>
+    <t>94764-8</t>
+  </si>
+  <si>
+    <t>SARS Coronavírus 2 [sequência de bases] genôma inteiro em isolado por sequenciamento</t>
+  </si>
+  <si>
     <t>94765-5</t>
   </si>
   <si>
@@ -504,6 +510,12 @@
     <t>SARS Coronavírus 2 [dosagem de] (carga viral) RNA em Amostra Inespecífica por Amplificação do ácido nucleico com detecção por sonda</t>
   </si>
   <si>
+    <t>94822-4</t>
+  </si>
+  <si>
+    <t>SARS Coronavírus 2 [Presença de] RNA em Saliva (fluido oral) por sequenciamento</t>
+  </si>
+  <si>
     <t>94845-5</t>
   </si>
   <si>
@@ -570,6 +582,12 @@
     <t>Vírus da Influenza A e B e SARS Coronavírus 2 identificado em  Amostra respiratória por Amplificação do ácido nucleico com detecção por sonda</t>
   </si>
   <si>
+    <t>95424-8</t>
+  </si>
+  <si>
+    <t>SARS Coronavírus 2 [Presença de] RNA em Amostra respiratória por sequenciamento</t>
+  </si>
+  <si>
     <t>95425-5</t>
   </si>
   <si>
@@ -618,6 +636,12 @@
     <t>SARS Coronavírus 2  [Presença de] RNA em amostra respiraória por Amplificação de ácido nucleico com detecção sem sonda</t>
   </si>
   <si>
+    <t>95609-4</t>
+  </si>
+  <si>
+    <t>SARS Coronavírus 2 [Presença de] gene S em amostra respiratória por sequenciação</t>
+  </si>
+  <si>
     <t>95823-1</t>
   </si>
   <si>
@@ -654,6 +678,12 @@
     <t>Vírus da Influenza A e B e SARS Coronavírus + SARS Coronavírus 2 painel de antígeno - Amostra de trato respiratório superior por Imunoensaio rápido</t>
   </si>
   <si>
+    <t>95970-0</t>
+  </si>
+  <si>
+    <t>SARS Coronavírus 2 rearranjos específicos de genes de células T de receptor beta [Presença de] em sangue por sequenciamento</t>
+  </si>
+  <si>
     <t>95971-8</t>
   </si>
   <si>
@@ -738,6 +768,12 @@
     <t>SARS Coronavírus 2 proteína S domínio de ligação ao RNA anticorpo neutralizante [Presença] em soro ou plasma por imunonensaio</t>
   </si>
   <si>
+    <t>96741-4</t>
+  </si>
+  <si>
+    <t>SARS Coronavírus 2 variante [Tipo] em espécie por sequenciação</t>
+  </si>
+  <si>
     <t>96742-2</t>
   </si>
   <si>
@@ -804,6 +840,12 @@
     <t>SARS coronavirus 2 painel de sequenciamento e identificação - Amostra pelo método de genética molecular</t>
   </si>
   <si>
+    <t>98062-3</t>
+  </si>
+  <si>
+    <t>Identificador de estudo de sequenciamento</t>
+  </si>
+  <si>
     <t>96895-8</t>
   </si>
   <si>
@@ -1816,6 +1858,60 @@
   </si>
   <si>
     <t>RNA do Vírus Sincicial Respiratório B [Presença] na amostra por amplificação de ácidos nucleicos com detecção por sonda</t>
+  </si>
+  <si>
+    <t>97314-9</t>
+  </si>
+  <si>
+    <t>DNA de Vibrio cholerae [Presença] nas fezes por amplificação de ácidos nucleicos com detecção por sonda</t>
+  </si>
+  <si>
+    <t>29658-2</t>
+  </si>
+  <si>
+    <t>Anticorpo IgM contra Bordetella pertussis [Presença] no soro por imunoensaio</t>
+  </si>
+  <si>
+    <t>91775-7</t>
+  </si>
+  <si>
+    <t>Bordetella sp. identificada em amostra do trato Respiratório inferior por meio de cultura específica para o organismo</t>
+  </si>
+  <si>
+    <t>63431-1</t>
+  </si>
+  <si>
+    <t>DNA de Bordetella sp. [Presença] na amostra por amplificação de ácidos nucleicos com detecção por sonda</t>
+  </si>
+  <si>
+    <t>62426-2</t>
+  </si>
+  <si>
+    <t>Painel de DNA de Bordetella sp. - Amostra por amplificação de ácidos nucleicos com detecção por sonda</t>
+  </si>
+  <si>
+    <t>62428-8</t>
+  </si>
+  <si>
+    <t>DNA de Bordetella sp. [Identificador] na amostra por amplificação de ácidos nucleicos com detecção por sonda</t>
+  </si>
+  <si>
+    <t>67561-1</t>
+  </si>
+  <si>
+    <t>DNA de Corynebacterium diphtheriae [Presença] na amostra por amplificação de ácidos nucleicos com detecção por sonda</t>
+  </si>
+  <si>
+    <t>88584-8</t>
+  </si>
+  <si>
+    <t>Corynebacterium diphtheriae [Presença] em amostra das vias respiratórias superiores por cultura específica do organismo</t>
+  </si>
+  <si>
+    <t>6581-3</t>
+  </si>
+  <si>
+    <t>Vibrio sp. identificado na amostra por meio de cultura específica para o organismo</t>
   </si>
 </sst>
 </file>
@@ -2123,7 +2219,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D281"/>
+  <dimension ref="A1:D297"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -5500,6 +5596,198 @@
       </c>
       <c r="D281" s="2"/>
     </row>
+    <row r="282">
+      <c r="A282" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B282" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="C282" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="D282" s="2"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B283" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="C283" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="D283" s="2"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B284" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="C284" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="D284" s="2"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B285" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="C285" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="D285" s="2"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B286" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="C286" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="D286" s="2"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B287" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="C287" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="D287" s="2"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B288" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="C288" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="D288" s="2"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B289" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="C289" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="D289" s="2"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B290" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="C290" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="D290" s="2"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B291" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="C291" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="D291" s="2"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B292" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="C292" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="D292" s="2"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B293" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="C293" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="D293" s="2"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B294" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="C294" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="D294" s="2"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B295" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="C295" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="D295" s="2"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B296" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="C296" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="D296" s="2"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B297" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="C297" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="D297" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
